--- a/Courses/Term 3/SCM/Case Studies/SIKA_Solver.xlsx
+++ b/Courses/Term 3/SCM/Case Studies/SIKA_Solver.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MBA\Courses\Term 3\SCM\Case Studies\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDB38E15-01C0-4383-8782-C7578E6A6015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F94D07E8-E53C-46CF-B773-DFD4D72DEBE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -261,7 +261,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -272,6 +272,7 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -579,7 +580,8 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="9" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="9" width="9.77734375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5.33203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="15.88671875" bestFit="1" customWidth="1"/>
@@ -716,7 +718,7 @@
         <v>1050000</v>
       </c>
       <c r="N3">
-        <f t="shared" ref="N3:N9" si="1">K3*L3</f>
+        <f t="shared" ref="N3:N7" si="1">K3*L3</f>
         <v>800</v>
       </c>
     </row>
@@ -803,7 +805,7 @@
         <v>483</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" s="3">
         <f>618240</f>
@@ -811,7 +813,7 @@
       </c>
       <c r="N5">
         <f t="shared" si="1"/>
-        <v>483</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
@@ -1178,9 +1180,9 @@
       <c r="A20" t="s">
         <v>34</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="4">
         <f>SUMPRODUCT(B2:I7, B12:I17) + SUMPRODUCT(M2:M7, L2:L7)</f>
-        <v>47337913.600000001</v>
+        <v>46719673.600000001</v>
       </c>
     </row>
   </sheetData>
